--- a/analysis_output/金相定量表征数据汇总.xlsx
+++ b/analysis_output/金相定量表征数据汇总.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:AD57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,45 +439,130 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>像素尺寸(μm/像素)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>校准来源</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>图像宽度(像素)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>图像高度(像素)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>通道数</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>视野宽度(μm)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>视野高度(μm)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>视野面积(μm²)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>相机型号</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>拍摄日期</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>总物理面积(μm²)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>背景/基体面积占比(%)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>背景/基体物理面积(μm²)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>熔覆层组织面积占比(%)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>熔覆层组织物理面积(μm²)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>析出相/碳化物面积占比(%)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>析出相/碳化物物理面积(μm²)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>气孔缺陷面积占比(%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>气孔缺陷物理面积(μm²)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>裂纹缺陷面积占比(%)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>裂纹缺陷物理面积(μm²)</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>气孔孔隙率(%)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>微裂纹面积占比(%)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>熔覆层平均晶粒尺寸(μm)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>熔覆层平均晶粒面积(μm²)</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>基体稀释率(%)</t>
         </is>
@@ -501,30 +586,87 @@
         <v>4915200</v>
       </c>
       <c r="E2" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:04:51</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P2" t="n">
         <v>30.192</v>
       </c>
-      <c r="F2" t="n">
+      <c r="Q2" t="n">
+        <v>1055112.05</v>
+      </c>
+      <c r="R2" t="n">
         <v>54.573</v>
       </c>
-      <c r="G2" t="n">
+      <c r="S2" t="n">
+        <v>1907141.23</v>
+      </c>
+      <c r="T2" t="n">
         <v>14.027</v>
       </c>
-      <c r="H2" t="n">
+      <c r="U2" t="n">
+        <v>490194.67</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.908</v>
       </c>
-      <c r="I2" t="n">
+      <c r="W2" t="n">
+        <v>31725.3</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.301</v>
       </c>
-      <c r="J2" t="n">
+      <c r="Y2" t="n">
+        <v>10508.5</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.908</v>
       </c>
-      <c r="K2" t="n">
+      <c r="AA2" t="n">
         <v>0.301</v>
       </c>
-      <c r="L2" t="n">
-        <v>59.97</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="AB2" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2556.65</v>
+      </c>
+      <c r="AD2" t="n">
         <v>35.62</v>
       </c>
     </row>
@@ -546,30 +688,87 @@
         <v>4915200</v>
       </c>
       <c r="E3" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:05:44</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P3" t="n">
         <v>29.726</v>
       </c>
-      <c r="F3" t="n">
+      <c r="Q3" t="n">
+        <v>1038843.07</v>
+      </c>
+      <c r="R3" t="n">
         <v>55.584</v>
       </c>
-      <c r="G3" t="n">
+      <c r="S3" t="n">
+        <v>1942484.78</v>
+      </c>
+      <c r="T3" t="n">
         <v>13.27</v>
       </c>
-      <c r="H3" t="n">
+      <c r="U3" t="n">
+        <v>463744.95</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.779</v>
       </c>
-      <c r="I3" t="n">
+      <c r="W3" t="n">
+        <v>27228.97</v>
+      </c>
+      <c r="X3" t="n">
         <v>0.64</v>
       </c>
-      <c r="J3" t="n">
+      <c r="Y3" t="n">
+        <v>22379.98</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.779</v>
       </c>
-      <c r="K3" t="n">
+      <c r="AA3" t="n">
         <v>0.64</v>
       </c>
-      <c r="L3" t="n">
-        <v>54.47</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="AB3" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2109.72</v>
+      </c>
+      <c r="AD3" t="n">
         <v>34.84</v>
       </c>
     </row>
@@ -591,30 +790,67 @@
         <v>4915200</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>放大倍数估算</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>4915200</v>
+      </c>
+      <c r="P4" t="n">
         <v>31.038</v>
       </c>
-      <c r="F4" t="n">
+      <c r="Q4" t="n">
+        <v>1525568</v>
+      </c>
+      <c r="R4" t="n">
         <v>53.598</v>
       </c>
-      <c r="G4" t="n">
+      <c r="S4" t="n">
+        <v>2634451</v>
+      </c>
+      <c r="T4" t="n">
         <v>14.168</v>
       </c>
-      <c r="H4" t="n">
+      <c r="U4" t="n">
+        <v>696370</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.657</v>
       </c>
-      <c r="I4" t="n">
+      <c r="W4" t="n">
+        <v>32299</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.539</v>
       </c>
-      <c r="J4" t="n">
+      <c r="Y4" t="n">
+        <v>26512</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.657</v>
       </c>
-      <c r="K4" t="n">
+      <c r="AA4" t="n">
         <v>0.539</v>
       </c>
-      <c r="L4" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="AB4" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3058.44</v>
+      </c>
+      <c r="AD4" t="n">
         <v>36.67</v>
       </c>
     </row>
@@ -636,30 +872,87 @@
         <v>4915200</v>
       </c>
       <c r="E5" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:06:41</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P5" t="n">
         <v>30.802</v>
       </c>
-      <c r="F5" t="n">
+      <c r="Q5" t="n">
+        <v>1076446.87</v>
+      </c>
+      <c r="R5" t="n">
         <v>53.694</v>
       </c>
-      <c r="G5" t="n">
+      <c r="S5" t="n">
+        <v>1876421.99</v>
+      </c>
+      <c r="T5" t="n">
         <v>14.535</v>
       </c>
-      <c r="H5" t="n">
+      <c r="U5" t="n">
+        <v>507967.41</v>
+      </c>
+      <c r="V5" t="n">
         <v>0.422</v>
       </c>
-      <c r="I5" t="n">
+      <c r="W5" t="n">
+        <v>14760.96</v>
+      </c>
+      <c r="X5" t="n">
         <v>0.546</v>
       </c>
-      <c r="J5" t="n">
+      <c r="Y5" t="n">
+        <v>19084.52</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.422</v>
       </c>
-      <c r="K5" t="n">
+      <c r="AA5" t="n">
         <v>0.546</v>
       </c>
-      <c r="L5" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AB5" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2419.11</v>
+      </c>
+      <c r="AD5" t="n">
         <v>36.45</v>
       </c>
     </row>
@@ -681,30 +974,87 @@
         <v>4915200</v>
       </c>
       <c r="E6" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:07:11</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P6" t="n">
         <v>30.489</v>
       </c>
-      <c r="F6" t="n">
+      <c r="Q6" t="n">
+        <v>1065489.73</v>
+      </c>
+      <c r="R6" t="n">
         <v>55.214</v>
       </c>
-      <c r="G6" t="n">
+      <c r="S6" t="n">
+        <v>1929536.86</v>
+      </c>
+      <c r="T6" t="n">
         <v>13.493</v>
       </c>
-      <c r="H6" t="n">
+      <c r="U6" t="n">
+        <v>471537.46</v>
+      </c>
+      <c r="V6" t="n">
         <v>0.262</v>
       </c>
-      <c r="I6" t="n">
+      <c r="W6" t="n">
+        <v>9139.84</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.543</v>
       </c>
-      <c r="J6" t="n">
+      <c r="Y6" t="n">
+        <v>18977.87</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.262</v>
       </c>
-      <c r="K6" t="n">
+      <c r="AA6" t="n">
         <v>0.543</v>
       </c>
-      <c r="L6" t="n">
-        <v>62.65</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="AB6" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2791</v>
+      </c>
+      <c r="AD6" t="n">
         <v>35.58</v>
       </c>
     </row>
@@ -726,30 +1076,87 @@
         <v>4915200</v>
       </c>
       <c r="E7" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026/5/7 18:56:03</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P7" t="n">
         <v>29.411</v>
       </c>
-      <c r="F7" t="n">
+      <c r="Q7" t="n">
+        <v>1027829.76</v>
+      </c>
+      <c r="R7" t="n">
         <v>55.406</v>
       </c>
-      <c r="G7" t="n">
+      <c r="S7" t="n">
+        <v>1936272.11</v>
+      </c>
+      <c r="T7" t="n">
         <v>14.397</v>
       </c>
-      <c r="H7" t="n">
+      <c r="U7" t="n">
+        <v>503136.2</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.652</v>
       </c>
-      <c r="I7" t="n">
+      <c r="W7" t="n">
+        <v>22772.45</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.134</v>
       </c>
-      <c r="J7" t="n">
+      <c r="Y7" t="n">
+        <v>4671.24</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.652</v>
       </c>
-      <c r="K7" t="n">
+      <c r="AA7" t="n">
         <v>0.134</v>
       </c>
-      <c r="L7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="AB7" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>756.1900000000001</v>
+      </c>
+      <c r="AD7" t="n">
         <v>34.68</v>
       </c>
     </row>
@@ -771,30 +1178,87 @@
         <v>4915200</v>
       </c>
       <c r="E8" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026/5/7 18:57:05</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P8" t="n">
         <v>30.093</v>
       </c>
-      <c r="F8" t="n">
+      <c r="Q8" t="n">
+        <v>1051658.75</v>
+      </c>
+      <c r="R8" t="n">
         <v>54.844</v>
       </c>
-      <c r="G8" t="n">
+      <c r="S8" t="n">
+        <v>1916611.68</v>
+      </c>
+      <c r="T8" t="n">
         <v>14.688</v>
       </c>
-      <c r="H8" t="n">
+      <c r="U8" t="n">
+        <v>513294.18</v>
+      </c>
+      <c r="V8" t="n">
         <v>0.331</v>
       </c>
-      <c r="I8" t="n">
+      <c r="W8" t="n">
+        <v>11570.02</v>
+      </c>
+      <c r="X8" t="n">
         <v>0.044</v>
       </c>
-      <c r="J8" t="n">
+      <c r="Y8" t="n">
+        <v>1547.12</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.331</v>
       </c>
-      <c r="K8" t="n">
+      <c r="AA8" t="n">
         <v>0.044</v>
       </c>
-      <c r="L8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="AB8" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>587.01</v>
+      </c>
+      <c r="AD8" t="n">
         <v>35.43</v>
       </c>
     </row>
@@ -816,30 +1280,87 @@
         <v>4915200</v>
       </c>
       <c r="E9" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026/5/7 18:57:41</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P9" t="n">
         <v>30.313</v>
       </c>
-      <c r="F9" t="n">
+      <c r="Q9" t="n">
+        <v>1059331.1</v>
+      </c>
+      <c r="R9" t="n">
         <v>55.206</v>
       </c>
-      <c r="G9" t="n">
+      <c r="S9" t="n">
+        <v>1929281.61</v>
+      </c>
+      <c r="T9" t="n">
         <v>14.24</v>
       </c>
-      <c r="H9" t="n">
+      <c r="U9" t="n">
+        <v>497633.1</v>
+      </c>
+      <c r="V9" t="n">
         <v>0.171</v>
       </c>
-      <c r="I9" t="n">
+      <c r="W9" t="n">
+        <v>5966.67</v>
+      </c>
+      <c r="X9" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="J9" t="n">
+      <c r="Y9" t="n">
+        <v>2469.29</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.171</v>
       </c>
-      <c r="K9" t="n">
+      <c r="AA9" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="L9" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="AB9" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>500.59</v>
+      </c>
+      <c r="AD9" t="n">
         <v>35.45</v>
       </c>
     </row>
@@ -861,30 +1382,87 @@
         <v>4915200</v>
       </c>
       <c r="E10" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026/5/7 18:59:05</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P10" t="n">
         <v>30.629</v>
       </c>
-      <c r="F10" t="n">
+      <c r="Q10" t="n">
+        <v>1070396.31</v>
+      </c>
+      <c r="R10" t="n">
         <v>54.511</v>
       </c>
-      <c r="G10" t="n">
+      <c r="S10" t="n">
+        <v>1904989.05</v>
+      </c>
+      <c r="T10" t="n">
         <v>14.509</v>
       </c>
-      <c r="H10" t="n">
+      <c r="U10" t="n">
+        <v>507033.16</v>
+      </c>
+      <c r="V10" t="n">
         <v>0.218</v>
       </c>
-      <c r="I10" t="n">
+      <c r="W10" t="n">
+        <v>7606.22</v>
+      </c>
+      <c r="X10" t="n">
         <v>0.133</v>
       </c>
-      <c r="J10" t="n">
+      <c r="Y10" t="n">
+        <v>4657.02</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.218</v>
       </c>
-      <c r="K10" t="n">
+      <c r="AA10" t="n">
         <v>0.133</v>
       </c>
-      <c r="L10" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="AB10" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>599.34</v>
+      </c>
+      <c r="AD10" t="n">
         <v>35.98</v>
       </c>
     </row>
@@ -906,30 +1484,87 @@
         <v>4915200</v>
       </c>
       <c r="E11" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:00:37</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P11" t="n">
         <v>29.661</v>
       </c>
-      <c r="F11" t="n">
+      <c r="Q11" t="n">
+        <v>1036562.2</v>
+      </c>
+      <c r="R11" t="n">
         <v>54.913</v>
       </c>
-      <c r="G11" t="n">
+      <c r="S11" t="n">
+        <v>1919035.46</v>
+      </c>
+      <c r="T11" t="n">
         <v>14.461</v>
       </c>
-      <c r="H11" t="n">
+      <c r="U11" t="n">
+        <v>505353.08</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.522</v>
       </c>
-      <c r="I11" t="n">
+      <c r="W11" t="n">
+        <v>18237.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.443</v>
       </c>
-      <c r="J11" t="n">
+      <c r="Y11" t="n">
+        <v>15494</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.522</v>
       </c>
-      <c r="K11" t="n">
+      <c r="AA11" t="n">
         <v>0.443</v>
       </c>
-      <c r="L11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="AB11" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2229.37</v>
+      </c>
+      <c r="AD11" t="n">
         <v>35.07</v>
       </c>
     </row>
@@ -951,30 +1586,87 @@
         <v>4915200</v>
       </c>
       <c r="E12" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:01:49</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P12" t="n">
         <v>30.868</v>
       </c>
-      <c r="F12" t="n">
+      <c r="Q12" t="n">
+        <v>1078744.81</v>
+      </c>
+      <c r="R12" t="n">
         <v>54.108</v>
       </c>
-      <c r="G12" t="n">
+      <c r="S12" t="n">
+        <v>1890913.49</v>
+      </c>
+      <c r="T12" t="n">
         <v>14.122</v>
       </c>
-      <c r="H12" t="n">
+      <c r="U12" t="n">
+        <v>493523.55</v>
+      </c>
+      <c r="V12" t="n">
         <v>0.409</v>
       </c>
-      <c r="I12" t="n">
+      <c r="W12" t="n">
+        <v>14285.31</v>
+      </c>
+      <c r="X12" t="n">
         <v>0.493</v>
       </c>
-      <c r="J12" t="n">
+      <c r="Y12" t="n">
+        <v>17214.61</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.409</v>
       </c>
-      <c r="K12" t="n">
+      <c r="AA12" t="n">
         <v>0.493</v>
       </c>
-      <c r="L12" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="AB12" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1640.26</v>
+      </c>
+      <c r="AD12" t="n">
         <v>36.33</v>
       </c>
     </row>
@@ -996,30 +1688,87 @@
         <v>4915200</v>
       </c>
       <c r="E13" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:02:57</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P13" t="n">
         <v>30.818</v>
       </c>
-      <c r="F13" t="n">
+      <c r="Q13" t="n">
+        <v>1076987.94</v>
+      </c>
+      <c r="R13" t="n">
         <v>55.398</v>
       </c>
-      <c r="G13" t="n">
+      <c r="S13" t="n">
+        <v>1935974.92</v>
+      </c>
+      <c r="T13" t="n">
         <v>13.301</v>
       </c>
-      <c r="H13" t="n">
+      <c r="U13" t="n">
+        <v>464843.44</v>
+      </c>
+      <c r="V13" t="n">
         <v>0.356</v>
       </c>
-      <c r="I13" t="n">
+      <c r="W13" t="n">
+        <v>12445.96</v>
+      </c>
+      <c r="X13" t="n">
         <v>0.127</v>
       </c>
-      <c r="J13" t="n">
+      <c r="Y13" t="n">
+        <v>4429.5</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.356</v>
       </c>
-      <c r="K13" t="n">
+      <c r="AA13" t="n">
         <v>0.127</v>
       </c>
-      <c r="L13" t="n">
-        <v>23.34</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="AB13" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1549.7</v>
+      </c>
+      <c r="AD13" t="n">
         <v>35.75</v>
       </c>
     </row>
@@ -1041,30 +1790,87 @@
         <v>4915200</v>
       </c>
       <c r="E14" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:03:27</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P14" t="n">
         <v>30.137</v>
       </c>
-      <c r="F14" t="n">
+      <c r="Q14" t="n">
+        <v>1053176.72</v>
+      </c>
+      <c r="R14" t="n">
         <v>55.446</v>
       </c>
-      <c r="G14" t="n">
+      <c r="S14" t="n">
+        <v>1937674.19</v>
+      </c>
+      <c r="T14" t="n">
         <v>13.784</v>
       </c>
-      <c r="H14" t="n">
+      <c r="U14" t="n">
+        <v>481692.59</v>
+      </c>
+      <c r="V14" t="n">
         <v>0.254</v>
       </c>
-      <c r="I14" t="n">
+      <c r="W14" t="n">
+        <v>8890.280000000001</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.379</v>
       </c>
-      <c r="J14" t="n">
+      <c r="Y14" t="n">
+        <v>13247.97</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.254</v>
       </c>
-      <c r="K14" t="n">
+      <c r="AA14" t="n">
         <v>0.379</v>
       </c>
-      <c r="L14" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="AB14" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2277.12</v>
+      </c>
+      <c r="AD14" t="n">
         <v>35.21</v>
       </c>
     </row>
@@ -1086,30 +1892,67 @@
         <v>4915200</v>
       </c>
       <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>放大倍数估算</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>1228800</v>
+      </c>
+      <c r="P15" t="n">
         <v>31.298</v>
       </c>
-      <c r="F15" t="n">
+      <c r="Q15" t="n">
+        <v>384593.5</v>
+      </c>
+      <c r="R15" t="n">
         <v>54.038</v>
       </c>
-      <c r="G15" t="n">
+      <c r="S15" t="n">
+        <v>664020</v>
+      </c>
+      <c r="T15" t="n">
         <v>13.756</v>
       </c>
-      <c r="H15" t="n">
+      <c r="U15" t="n">
+        <v>169030</v>
+      </c>
+      <c r="V15" t="n">
         <v>0.5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="W15" t="n">
+        <v>6141.75</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.408</v>
       </c>
-      <c r="J15" t="n">
+      <c r="Y15" t="n">
+        <v>5014.75</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K15" t="n">
+      <c r="AA15" t="n">
         <v>0.408</v>
       </c>
-      <c r="L15" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="AB15" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>482.04</v>
+      </c>
+      <c r="AD15" t="n">
         <v>36.68</v>
       </c>
     </row>
@@ -1131,30 +1974,87 @@
         <v>4915200</v>
       </c>
       <c r="E16" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026/5/7 18:54:42</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P16" t="n">
         <v>30.701</v>
       </c>
-      <c r="F16" t="n">
+      <c r="Q16" t="n">
+        <v>1072906.12</v>
+      </c>
+      <c r="R16" t="n">
         <v>54.446</v>
       </c>
-      <c r="G16" t="n">
+      <c r="S16" t="n">
+        <v>1902698.94</v>
+      </c>
+      <c r="T16" t="n">
         <v>14.796</v>
       </c>
-      <c r="H16" t="n">
+      <c r="U16" t="n">
+        <v>517065.3</v>
+      </c>
+      <c r="V16" t="n">
         <v>0.008</v>
       </c>
-      <c r="I16" t="n">
+      <c r="W16" t="n">
+        <v>277.29</v>
+      </c>
+      <c r="X16" t="n">
         <v>0.05</v>
       </c>
-      <c r="J16" t="n">
+      <c r="Y16" t="n">
+        <v>1734.12</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.008</v>
       </c>
-      <c r="K16" t="n">
+      <c r="AA16" t="n">
         <v>0.05</v>
       </c>
-      <c r="L16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="AB16" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1552.66</v>
+      </c>
+      <c r="AD16" t="n">
         <v>36.06</v>
       </c>
     </row>
@@ -1176,30 +2076,87 @@
         <v>4915200</v>
       </c>
       <c r="E17" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:18:29</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P17" t="n">
         <v>30.628</v>
       </c>
-      <c r="F17" t="n">
+      <c r="Q17" t="n">
+        <v>1070354.36</v>
+      </c>
+      <c r="R17" t="n">
         <v>54.703</v>
       </c>
-      <c r="G17" t="n">
+      <c r="S17" t="n">
+        <v>1911698</v>
+      </c>
+      <c r="T17" t="n">
         <v>14.234</v>
       </c>
-      <c r="H17" t="n">
+      <c r="U17" t="n">
+        <v>497421.22</v>
+      </c>
+      <c r="V17" t="n">
         <v>0.272</v>
       </c>
-      <c r="I17" t="n">
+      <c r="W17" t="n">
+        <v>9505.290000000001</v>
+      </c>
+      <c r="X17" t="n">
         <v>0.163</v>
       </c>
-      <c r="J17" t="n">
+      <c r="Y17" t="n">
+        <v>5702.89</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.272</v>
       </c>
-      <c r="K17" t="n">
+      <c r="AA17" t="n">
         <v>0.163</v>
       </c>
-      <c r="L17" t="n">
-        <v>81.23999999999999</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="AB17" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4692.56</v>
+      </c>
+      <c r="AD17" t="n">
         <v>35.89</v>
       </c>
     </row>
@@ -1221,30 +2178,87 @@
         <v>4915200</v>
       </c>
       <c r="E18" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:18:56</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P18" t="n">
         <v>31.679</v>
       </c>
-      <c r="F18" t="n">
+      <c r="Q18" t="n">
+        <v>1107065.16</v>
+      </c>
+      <c r="R18" t="n">
         <v>54.132</v>
       </c>
-      <c r="G18" t="n">
+      <c r="S18" t="n">
+        <v>1891749.62</v>
+      </c>
+      <c r="T18" t="n">
         <v>13.623</v>
       </c>
-      <c r="H18" t="n">
+      <c r="U18" t="n">
+        <v>476081.42</v>
+      </c>
+      <c r="V18" t="n">
         <v>0.205</v>
       </c>
-      <c r="I18" t="n">
+      <c r="W18" t="n">
+        <v>7163.98</v>
+      </c>
+      <c r="X18" t="n">
         <v>0.361</v>
       </c>
-      <c r="J18" t="n">
+      <c r="Y18" t="n">
+        <v>12621.58</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.205</v>
       </c>
-      <c r="K18" t="n">
+      <c r="AA18" t="n">
         <v>0.361</v>
       </c>
-      <c r="L18" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="AB18" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1534.9</v>
+      </c>
+      <c r="AD18" t="n">
         <v>36.92</v>
       </c>
     </row>
@@ -1266,30 +2280,67 @@
         <v>4915200</v>
       </c>
       <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>放大倍数估算</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>4915200</v>
+      </c>
+      <c r="P19" t="n">
         <v>30.324</v>
       </c>
-      <c r="F19" t="n">
+      <c r="Q19" t="n">
+        <v>1490478</v>
+      </c>
+      <c r="R19" t="n">
         <v>56.554</v>
       </c>
-      <c r="G19" t="n">
+      <c r="S19" t="n">
+        <v>2779754</v>
+      </c>
+      <c r="T19" t="n">
         <v>12.56</v>
       </c>
-      <c r="H19" t="n">
+      <c r="U19" t="n">
+        <v>617344</v>
+      </c>
+      <c r="V19" t="n">
         <v>0.194</v>
       </c>
-      <c r="I19" t="n">
+      <c r="W19" t="n">
+        <v>9531</v>
+      </c>
+      <c r="X19" t="n">
         <v>0.368</v>
       </c>
-      <c r="J19" t="n">
+      <c r="Y19" t="n">
+        <v>18093</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.194</v>
       </c>
-      <c r="K19" t="n">
+      <c r="AA19" t="n">
         <v>0.368</v>
       </c>
-      <c r="L19" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="AB19" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2156.35</v>
+      </c>
+      <c r="AD19" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -1311,30 +2362,87 @@
         <v>4915200</v>
       </c>
       <c r="E20" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:19:41</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P20" t="n">
         <v>30.715</v>
       </c>
-      <c r="F20" t="n">
+      <c r="Q20" t="n">
+        <v>1073396.71</v>
+      </c>
+      <c r="R20" t="n">
         <v>55.913</v>
       </c>
-      <c r="G20" t="n">
+      <c r="S20" t="n">
+        <v>1953975.88</v>
+      </c>
+      <c r="T20" t="n">
         <v>12.916</v>
       </c>
-      <c r="H20" t="n">
+      <c r="U20" t="n">
+        <v>451370.09</v>
+      </c>
+      <c r="V20" t="n">
         <v>0.125</v>
       </c>
-      <c r="I20" t="n">
+      <c r="W20" t="n">
+        <v>4359.11</v>
+      </c>
+      <c r="X20" t="n">
         <v>0.331</v>
       </c>
-      <c r="J20" t="n">
+      <c r="Y20" t="n">
+        <v>11579.97</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.125</v>
       </c>
-      <c r="K20" t="n">
+      <c r="AA20" t="n">
         <v>0.331</v>
       </c>
-      <c r="L20" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="AB20" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1592.98</v>
+      </c>
+      <c r="AD20" t="n">
         <v>35.46</v>
       </c>
     </row>
@@ -1356,30 +2464,87 @@
         <v>4915200</v>
       </c>
       <c r="E21" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:20:23</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P21" t="n">
         <v>29.861</v>
       </c>
-      <c r="F21" t="n">
+      <c r="Q21" t="n">
+        <v>1043555.54</v>
+      </c>
+      <c r="R21" t="n">
         <v>56.942</v>
       </c>
-      <c r="G21" t="n">
+      <c r="S21" t="n">
+        <v>1989935.16</v>
+      </c>
+      <c r="T21" t="n">
         <v>12.729</v>
       </c>
-      <c r="H21" t="n">
+      <c r="U21" t="n">
+        <v>444834.62</v>
+      </c>
+      <c r="V21" t="n">
         <v>0.104</v>
       </c>
-      <c r="I21" t="n">
+      <c r="W21" t="n">
+        <v>3625.36</v>
+      </c>
+      <c r="X21" t="n">
         <v>0.364</v>
       </c>
-      <c r="J21" t="n">
+      <c r="Y21" t="n">
+        <v>12731.07</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.104</v>
       </c>
-      <c r="K21" t="n">
+      <c r="AA21" t="n">
         <v>0.364</v>
       </c>
-      <c r="L21" t="n">
-        <v>46.96</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="AB21" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1567.75</v>
+      </c>
+      <c r="AD21" t="n">
         <v>34.4</v>
       </c>
     </row>
@@ -1401,30 +2566,87 @@
         <v>4915200</v>
       </c>
       <c r="E22" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:12:46</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P22" t="n">
         <v>29.316</v>
       </c>
-      <c r="F22" t="n">
+      <c r="Q22" t="n">
+        <v>1024517.95</v>
+      </c>
+      <c r="R22" t="n">
         <v>54.544</v>
       </c>
-      <c r="G22" t="n">
+      <c r="S22" t="n">
+        <v>1906135.17</v>
+      </c>
+      <c r="T22" t="n">
         <v>14.732</v>
       </c>
-      <c r="H22" t="n">
+      <c r="U22" t="n">
+        <v>514844.86</v>
+      </c>
+      <c r="V22" t="n">
         <v>0.58</v>
       </c>
-      <c r="I22" t="n">
+      <c r="W22" t="n">
+        <v>20258.38</v>
+      </c>
+      <c r="X22" t="n">
         <v>0.828</v>
       </c>
-      <c r="J22" t="n">
+      <c r="Y22" t="n">
+        <v>28925.4</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.58</v>
       </c>
-      <c r="K22" t="n">
+      <c r="AA22" t="n">
         <v>0.828</v>
       </c>
-      <c r="L22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="AB22" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>515.02</v>
+      </c>
+      <c r="AD22" t="n">
         <v>34.96</v>
       </c>
     </row>
@@ -1446,30 +2668,87 @@
         <v>4915200</v>
       </c>
       <c r="E23" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:13:42</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P23" t="n">
         <v>29.28</v>
       </c>
-      <c r="F23" t="n">
+      <c r="Q23" t="n">
+        <v>1023253.8</v>
+      </c>
+      <c r="R23" t="n">
         <v>54.645</v>
       </c>
-      <c r="G23" t="n">
+      <c r="S23" t="n">
+        <v>1909655.31</v>
+      </c>
+      <c r="T23" t="n">
         <v>14.291</v>
       </c>
-      <c r="H23" t="n">
+      <c r="U23" t="n">
+        <v>499429.78</v>
+      </c>
+      <c r="V23" t="n">
         <v>0.476</v>
       </c>
-      <c r="I23" t="n">
+      <c r="W23" t="n">
+        <v>16617.37</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.308</v>
       </c>
-      <c r="J23" t="n">
+      <c r="Y23" t="n">
+        <v>45725.5</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.476</v>
       </c>
-      <c r="K23" t="n">
+      <c r="AA23" t="n">
         <v>1.308</v>
       </c>
-      <c r="L23" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="AB23" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>672.6</v>
+      </c>
+      <c r="AD23" t="n">
         <v>34.89</v>
       </c>
     </row>
@@ -1491,30 +2770,87 @@
         <v>4915200</v>
       </c>
       <c r="E24" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:14:22</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P24" t="n">
         <v>25.407</v>
       </c>
-      <c r="F24" t="n">
+      <c r="Q24" t="n">
+        <v>887897.45</v>
+      </c>
+      <c r="R24" t="n">
         <v>54.206</v>
       </c>
-      <c r="G24" t="n">
+      <c r="S24" t="n">
+        <v>1894336.93</v>
+      </c>
+      <c r="T24" t="n">
         <v>13.551</v>
       </c>
-      <c r="H24" t="n">
+      <c r="U24" t="n">
+        <v>473550.99</v>
+      </c>
+      <c r="V24" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="I24" t="n">
+      <c r="W24" t="n">
+        <v>3053.01</v>
+      </c>
+      <c r="X24" t="n">
         <v>6.749</v>
       </c>
-      <c r="J24" t="n">
+      <c r="Y24" t="n">
+        <v>235843.38</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="K24" t="n">
+      <c r="AA24" t="n">
         <v>6.749</v>
       </c>
-      <c r="L24" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="AB24" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>971.4</v>
+      </c>
+      <c r="AD24" t="n">
         <v>31.91</v>
       </c>
     </row>
@@ -1536,30 +2872,87 @@
         <v>4915200</v>
       </c>
       <c r="E25" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:14:52</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P25" t="n">
         <v>26.925</v>
       </c>
-      <c r="F25" t="n">
+      <c r="Q25" t="n">
+        <v>940936.24</v>
+      </c>
+      <c r="R25" t="n">
         <v>53.063</v>
       </c>
-      <c r="G25" t="n">
+      <c r="S25" t="n">
+        <v>1854397.5</v>
+      </c>
+      <c r="T25" t="n">
         <v>13.767</v>
       </c>
-      <c r="H25" t="n">
+      <c r="U25" t="n">
+        <v>481106.73</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.117</v>
       </c>
-      <c r="I25" t="n">
+      <c r="W25" t="n">
+        <v>4076.84</v>
+      </c>
+      <c r="X25" t="n">
         <v>6.128</v>
       </c>
-      <c r="J25" t="n">
+      <c r="Y25" t="n">
+        <v>214164.44</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.117</v>
       </c>
-      <c r="K25" t="n">
+      <c r="AA25" t="n">
         <v>6.128</v>
       </c>
-      <c r="L25" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="AB25" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>733.17</v>
+      </c>
+      <c r="AD25" t="n">
         <v>33.66</v>
       </c>
     </row>
@@ -1581,30 +2974,87 @@
         <v>4915200</v>
       </c>
       <c r="E26" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:16:00</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P26" t="n">
         <v>31.504</v>
       </c>
-      <c r="F26" t="n">
+      <c r="Q26" t="n">
+        <v>1100953.44</v>
+      </c>
+      <c r="R26" t="n">
         <v>54.516</v>
       </c>
-      <c r="G26" t="n">
+      <c r="S26" t="n">
+        <v>1905170.35</v>
+      </c>
+      <c r="T26" t="n">
         <v>13.666</v>
       </c>
-      <c r="H26" t="n">
+      <c r="U26" t="n">
+        <v>477565.98</v>
+      </c>
+      <c r="V26" t="n">
         <v>0.307</v>
       </c>
-      <c r="I26" t="n">
+      <c r="W26" t="n">
+        <v>10714.69</v>
+      </c>
+      <c r="X26" t="n">
         <v>0.008</v>
       </c>
-      <c r="J26" t="n">
+      <c r="Y26" t="n">
+        <v>277.29</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.307</v>
       </c>
-      <c r="K26" t="n">
+      <c r="AA26" t="n">
         <v>0.008</v>
       </c>
-      <c r="L26" t="n">
-        <v>27.73</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="AB26" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2187.26</v>
+      </c>
+      <c r="AD26" t="n">
         <v>36.62</v>
       </c>
     </row>
@@ -1626,30 +3076,87 @@
         <v>4915200</v>
       </c>
       <c r="E27" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:16:37</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P27" t="n">
         <v>32.313</v>
       </c>
-      <c r="F27" t="n">
+      <c r="Q27" t="n">
+        <v>1129224.73</v>
+      </c>
+      <c r="R27" t="n">
         <v>55.043</v>
       </c>
-      <c r="G27" t="n">
+      <c r="S27" t="n">
+        <v>1923573.03</v>
+      </c>
+      <c r="T27" t="n">
         <v>12.372</v>
       </c>
-      <c r="H27" t="n">
+      <c r="U27" t="n">
+        <v>432363.06</v>
+      </c>
+      <c r="V27" t="n">
         <v>0.215</v>
       </c>
-      <c r="I27" t="n">
+      <c r="W27" t="n">
+        <v>7519.48</v>
+      </c>
+      <c r="X27" t="n">
         <v>0.057</v>
       </c>
-      <c r="J27" t="n">
+      <c r="Y27" t="n">
+        <v>2001.45</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.215</v>
       </c>
-      <c r="K27" t="n">
+      <c r="AA27" t="n">
         <v>0.057</v>
       </c>
-      <c r="L27" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="AB27" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1545.24</v>
+      </c>
+      <c r="AD27" t="n">
         <v>36.99</v>
       </c>
     </row>
@@ -1671,30 +3178,87 @@
         <v>4915200</v>
       </c>
       <c r="E28" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:17:38</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P28" t="n">
         <v>31.505</v>
       </c>
-      <c r="F28" t="n">
+      <c r="Q28" t="n">
+        <v>1100982.59</v>
+      </c>
+      <c r="R28" t="n">
         <v>53.86</v>
       </c>
-      <c r="G28" t="n">
+      <c r="S28" t="n">
+        <v>1882244.33</v>
+      </c>
+      <c r="T28" t="n">
         <v>14.46</v>
       </c>
-      <c r="H28" t="n">
+      <c r="U28" t="n">
+        <v>505342.42</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.125</v>
       </c>
-      <c r="I28" t="n">
+      <c r="W28" t="n">
+        <v>4362.66</v>
+      </c>
+      <c r="X28" t="n">
         <v>0.05</v>
       </c>
-      <c r="J28" t="n">
+      <c r="Y28" t="n">
+        <v>1749.76</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.125</v>
       </c>
-      <c r="K28" t="n">
+      <c r="AA28" t="n">
         <v>0.05</v>
       </c>
-      <c r="L28" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="AB28" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1133.64</v>
+      </c>
+      <c r="AD28" t="n">
         <v>36.91</v>
       </c>
     </row>
@@ -1716,30 +3280,87 @@
         <v>4915200</v>
       </c>
       <c r="E29" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:11:56</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P29" t="n">
         <v>30.248</v>
       </c>
-      <c r="F29" t="n">
+      <c r="Q29" t="n">
+        <v>1057077.95</v>
+      </c>
+      <c r="R29" t="n">
         <v>54.734</v>
       </c>
-      <c r="G29" t="n">
+      <c r="S29" t="n">
+        <v>1912778</v>
+      </c>
+      <c r="T29" t="n">
         <v>14.927</v>
       </c>
-      <c r="H29" t="n">
+      <c r="U29" t="n">
+        <v>521634.86</v>
+      </c>
+      <c r="V29" t="n">
         <v>0.004</v>
       </c>
-      <c r="I29" t="n">
+      <c r="W29" t="n">
+        <v>147.89</v>
+      </c>
+      <c r="X29" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="J29" t="n">
+      <c r="Y29" t="n">
+        <v>3043.06</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.004</v>
       </c>
-      <c r="K29" t="n">
+      <c r="AA29" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="L29" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="AB29" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4515.77</v>
+      </c>
+      <c r="AD29" t="n">
         <v>35.59</v>
       </c>
     </row>
@@ -1761,30 +3382,87 @@
         <v>4915200</v>
       </c>
       <c r="E30" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:35:22</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P30" t="n">
         <v>30.004</v>
       </c>
-      <c r="F30" t="n">
+      <c r="Q30" t="n">
+        <v>1048548.15</v>
+      </c>
+      <c r="R30" t="n">
         <v>55.409</v>
       </c>
-      <c r="G30" t="n">
+      <c r="S30" t="n">
+        <v>1936377.34</v>
+      </c>
+      <c r="T30" t="n">
         <v>13.798</v>
       </c>
-      <c r="H30" t="n">
+      <c r="U30" t="n">
+        <v>482197.4</v>
+      </c>
+      <c r="V30" t="n">
         <v>0.572</v>
       </c>
-      <c r="I30" t="n">
+      <c r="W30" t="n">
+        <v>19976.11</v>
+      </c>
+      <c r="X30" t="n">
         <v>0.217</v>
       </c>
-      <c r="J30" t="n">
+      <c r="Y30" t="n">
+        <v>7582.76</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.572</v>
       </c>
-      <c r="K30" t="n">
+      <c r="AA30" t="n">
         <v>0.217</v>
       </c>
-      <c r="L30" t="n">
-        <v>55.03</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="AB30" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2152.73</v>
+      </c>
+      <c r="AD30" t="n">
         <v>35.13</v>
       </c>
     </row>
@@ -1806,30 +3484,87 @@
         <v>4915200</v>
       </c>
       <c r="E31" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:35:49</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P31" t="n">
         <v>30.667</v>
       </c>
-      <c r="F31" t="n">
+      <c r="Q31" t="n">
+        <v>1071728</v>
+      </c>
+      <c r="R31" t="n">
         <v>54.971</v>
       </c>
-      <c r="G31" t="n">
+      <c r="S31" t="n">
+        <v>1921062.51</v>
+      </c>
+      <c r="T31" t="n">
         <v>13.728</v>
       </c>
-      <c r="H31" t="n">
+      <c r="U31" t="n">
+        <v>479740.2</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.34</v>
       </c>
-      <c r="I31" t="n">
+      <c r="W31" t="n">
+        <v>11890.68</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.294</v>
       </c>
-      <c r="J31" t="n">
+      <c r="Y31" t="n">
+        <v>10260.37</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.34</v>
       </c>
-      <c r="K31" t="n">
+      <c r="AA31" t="n">
         <v>0.294</v>
       </c>
-      <c r="L31" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="AB31" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2285.19</v>
+      </c>
+      <c r="AD31" t="n">
         <v>35.81</v>
       </c>
     </row>
@@ -1851,30 +3586,67 @@
         <v>4915200</v>
       </c>
       <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>放大倍数估算</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>4915200</v>
+      </c>
+      <c r="P32" t="n">
         <v>29.689</v>
       </c>
-      <c r="F32" t="n">
+      <c r="Q32" t="n">
+        <v>1459290</v>
+      </c>
+      <c r="R32" t="n">
         <v>55.981</v>
       </c>
-      <c r="G32" t="n">
+      <c r="S32" t="n">
+        <v>2751556</v>
+      </c>
+      <c r="T32" t="n">
         <v>13.71</v>
       </c>
-      <c r="H32" t="n">
+      <c r="U32" t="n">
+        <v>673897</v>
+      </c>
+      <c r="V32" t="n">
         <v>0.317</v>
       </c>
-      <c r="I32" t="n">
+      <c r="W32" t="n">
+        <v>15581</v>
+      </c>
+      <c r="X32" t="n">
         <v>0.303</v>
       </c>
-      <c r="J32" t="n">
+      <c r="Y32" t="n">
+        <v>14876</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.317</v>
       </c>
-      <c r="K32" t="n">
+      <c r="AA32" t="n">
         <v>0.303</v>
       </c>
-      <c r="L32" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="AB32" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3002.75</v>
+      </c>
+      <c r="AD32" t="n">
         <v>34.66</v>
       </c>
     </row>
@@ -1896,30 +3668,87 @@
         <v>4915200</v>
       </c>
       <c r="E33" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:36:40</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P33" t="n">
         <v>29.879</v>
       </c>
-      <c r="F33" t="n">
+      <c r="Q33" t="n">
+        <v>1044186.91</v>
+      </c>
+      <c r="R33" t="n">
         <v>54.914</v>
       </c>
-      <c r="G33" t="n">
+      <c r="S33" t="n">
+        <v>1919083.81</v>
+      </c>
+      <c r="T33" t="n">
         <v>14.818</v>
       </c>
-      <c r="H33" t="n">
+      <c r="U33" t="n">
+        <v>517843.13</v>
+      </c>
+      <c r="V33" t="n">
         <v>0.199</v>
       </c>
-      <c r="I33" t="n">
+      <c r="W33" t="n">
+        <v>6945</v>
+      </c>
+      <c r="X33" t="n">
         <v>0.19</v>
       </c>
-      <c r="J33" t="n">
+      <c r="Y33" t="n">
+        <v>6622.92</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.199</v>
       </c>
-      <c r="K33" t="n">
+      <c r="AA33" t="n">
         <v>0.19</v>
       </c>
-      <c r="L33" t="n">
-        <v>68.65000000000001</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="AB33" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3350.97</v>
+      </c>
+      <c r="AD33" t="n">
         <v>35.24</v>
       </c>
     </row>
@@ -1941,30 +3770,87 @@
         <v>4915200</v>
       </c>
       <c r="E34" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:36:57</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P34" t="n">
         <v>29.646</v>
       </c>
-      <c r="F34" t="n">
+      <c r="Q34" t="n">
+        <v>1036022.55</v>
+      </c>
+      <c r="R34" t="n">
         <v>56.056</v>
       </c>
-      <c r="G34" t="n">
+      <c r="S34" t="n">
+        <v>1958971.33</v>
+      </c>
+      <c r="T34" t="n">
         <v>13.734</v>
       </c>
-      <c r="H34" t="n">
+      <c r="U34" t="n">
+        <v>479949.95</v>
+      </c>
+      <c r="V34" t="n">
         <v>0.347</v>
       </c>
-      <c r="I34" t="n">
+      <c r="W34" t="n">
+        <v>12128.15</v>
+      </c>
+      <c r="X34" t="n">
         <v>0.218</v>
       </c>
-      <c r="J34" t="n">
+      <c r="Y34" t="n">
+        <v>7609.78</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.347</v>
       </c>
-      <c r="K34" t="n">
+      <c r="AA34" t="n">
         <v>0.218</v>
       </c>
-      <c r="L34" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="AB34" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3038.12</v>
+      </c>
+      <c r="AD34" t="n">
         <v>34.59</v>
       </c>
     </row>
@@ -1986,30 +3872,87 @@
         <v>4915200</v>
       </c>
       <c r="E35" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:25:23</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P35" t="n">
         <v>29.602</v>
       </c>
-      <c r="F35" t="n">
+      <c r="Q35" t="n">
+        <v>1034488.94</v>
+      </c>
+      <c r="R35" t="n">
         <v>54.462</v>
       </c>
-      <c r="G35" t="n">
+      <c r="S35" t="n">
+        <v>1903260.62</v>
+      </c>
+      <c r="T35" t="n">
         <v>14.801</v>
       </c>
-      <c r="H35" t="n">
+      <c r="U35" t="n">
+        <v>517247.31</v>
+      </c>
+      <c r="V35" t="n">
         <v>0.969</v>
       </c>
-      <c r="I35" t="n">
+      <c r="W35" t="n">
+        <v>33877.48</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.166</v>
       </c>
-      <c r="J35" t="n">
+      <c r="Y35" t="n">
+        <v>5807.41</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.969</v>
       </c>
-      <c r="K35" t="n">
+      <c r="AA35" t="n">
         <v>0.166</v>
       </c>
-      <c r="L35" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="AB35" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>842.4299999999999</v>
+      </c>
+      <c r="AD35" t="n">
         <v>35.21</v>
       </c>
     </row>
@@ -2031,30 +3974,87 @@
         <v>4915200</v>
       </c>
       <c r="E36" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:30:39</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P36" t="n">
         <v>29.485</v>
       </c>
-      <c r="F36" t="n">
+      <c r="Q36" t="n">
+        <v>1030422.05</v>
+      </c>
+      <c r="R36" t="n">
         <v>54.081</v>
       </c>
-      <c r="G36" t="n">
+      <c r="S36" t="n">
+        <v>1889950.8</v>
+      </c>
+      <c r="T36" t="n">
         <v>14.367</v>
       </c>
-      <c r="H36" t="n">
+      <c r="U36" t="n">
+        <v>502071.84</v>
+      </c>
+      <c r="V36" t="n">
         <v>0.674</v>
       </c>
-      <c r="I36" t="n">
+      <c r="W36" t="n">
+        <v>23560.95</v>
+      </c>
+      <c r="X36" t="n">
         <v>1.393</v>
       </c>
-      <c r="J36" t="n">
+      <c r="Y36" t="n">
+        <v>48676.13</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.674</v>
       </c>
-      <c r="K36" t="n">
+      <c r="AA36" t="n">
         <v>1.393</v>
       </c>
-      <c r="L36" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="AB36" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>794.08</v>
+      </c>
+      <c r="AD36" t="n">
         <v>35.28</v>
       </c>
     </row>
@@ -2076,30 +4076,87 @@
         <v>4915200</v>
       </c>
       <c r="E37" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:31:29</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P37" t="n">
         <v>30.371</v>
       </c>
-      <c r="F37" t="n">
+      <c r="Q37" t="n">
+        <v>1061371.65</v>
+      </c>
+      <c r="R37" t="n">
         <v>54.019</v>
       </c>
-      <c r="G37" t="n">
+      <c r="S37" t="n">
+        <v>1887792.22</v>
+      </c>
+      <c r="T37" t="n">
         <v>14.574</v>
       </c>
-      <c r="H37" t="n">
+      <c r="U37" t="n">
+        <v>509330.39</v>
+      </c>
+      <c r="V37" t="n">
         <v>0.605</v>
       </c>
-      <c r="I37" t="n">
+      <c r="W37" t="n">
+        <v>21140.01</v>
+      </c>
+      <c r="X37" t="n">
         <v>0.431</v>
       </c>
-      <c r="J37" t="n">
+      <c r="Y37" t="n">
+        <v>15047.49</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.605</v>
       </c>
-      <c r="K37" t="n">
+      <c r="AA37" t="n">
         <v>0.431</v>
       </c>
-      <c r="L37" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="AB37" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>542.11</v>
+      </c>
+      <c r="AD37" t="n">
         <v>35.99</v>
       </c>
     </row>
@@ -2121,30 +4178,87 @@
         <v>4915200</v>
       </c>
       <c r="E38" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:32:05</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P38" t="n">
         <v>29.731</v>
       </c>
-      <c r="F38" t="n">
+      <c r="Q38" t="n">
+        <v>1039014.42</v>
+      </c>
+      <c r="R38" t="n">
         <v>55.366</v>
       </c>
-      <c r="G38" t="n">
+      <c r="S38" t="n">
+        <v>1934860.79</v>
+      </c>
+      <c r="T38" t="n">
         <v>13.956</v>
       </c>
-      <c r="H38" t="n">
+      <c r="U38" t="n">
+        <v>487716.85</v>
+      </c>
+      <c r="V38" t="n">
         <v>0.378</v>
       </c>
-      <c r="I38" t="n">
+      <c r="W38" t="n">
+        <v>13213.13</v>
+      </c>
+      <c r="X38" t="n">
         <v>0.569</v>
       </c>
-      <c r="J38" t="n">
+      <c r="Y38" t="n">
+        <v>19876.57</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.378</v>
       </c>
-      <c r="K38" t="n">
+      <c r="AA38" t="n">
         <v>0.569</v>
       </c>
-      <c r="L38" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="AB38" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="AD38" t="n">
         <v>34.94</v>
       </c>
     </row>
@@ -2166,30 +4280,87 @@
         <v>4915200</v>
       </c>
       <c r="E39" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:34:32</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P39" t="n">
         <v>31.637</v>
       </c>
-      <c r="F39" t="n">
+      <c r="Q39" t="n">
+        <v>1105622.55</v>
+      </c>
+      <c r="R39" t="n">
         <v>54.479</v>
       </c>
-      <c r="G39" t="n">
+      <c r="S39" t="n">
+        <v>1903854.3</v>
+      </c>
+      <c r="T39" t="n">
         <v>13.674</v>
       </c>
-      <c r="H39" t="n">
+      <c r="U39" t="n">
+        <v>477849.67</v>
+      </c>
+      <c r="V39" t="n">
         <v>0.207</v>
       </c>
-      <c r="I39" t="n">
+      <c r="W39" t="n">
+        <v>7224.42</v>
+      </c>
+      <c r="X39" t="n">
         <v>0.004</v>
       </c>
-      <c r="J39" t="n">
+      <c r="Y39" t="n">
+        <v>130.82</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.207</v>
       </c>
-      <c r="K39" t="n">
+      <c r="AA39" t="n">
         <v>0.004</v>
       </c>
-      <c r="L39" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="AB39" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1528.43</v>
+      </c>
+      <c r="AD39" t="n">
         <v>36.74</v>
       </c>
     </row>
@@ -2211,30 +4382,87 @@
         <v>4915200</v>
       </c>
       <c r="E40" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:32:55</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P40" t="n">
         <v>30.553</v>
       </c>
-      <c r="F40" t="n">
+      <c r="Q40" t="n">
+        <v>1067742.16</v>
+      </c>
+      <c r="R40" t="n">
         <v>54.693</v>
       </c>
-      <c r="G40" t="n">
+      <c r="S40" t="n">
+        <v>1911353.88</v>
+      </c>
+      <c r="T40" t="n">
         <v>14.47</v>
       </c>
-      <c r="H40" t="n">
+      <c r="U40" t="n">
+        <v>505697.91</v>
+      </c>
+      <c r="V40" t="n">
         <v>0.282</v>
       </c>
-      <c r="I40" t="n">
+      <c r="W40" t="n">
+        <v>9841.59</v>
+      </c>
+      <c r="X40" t="n">
         <v>0.001</v>
       </c>
-      <c r="J40" t="n">
+      <c r="Y40" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.282</v>
       </c>
-      <c r="K40" t="n">
+      <c r="AA40" t="n">
         <v>0.001</v>
       </c>
-      <c r="L40" t="n">
-        <v>24.16</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="AB40" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1660.54</v>
+      </c>
+      <c r="AD40" t="n">
         <v>35.84</v>
       </c>
     </row>
@@ -2256,30 +4484,87 @@
         <v>4915200</v>
       </c>
       <c r="E41" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:33:26</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P41" t="n">
         <v>32.141</v>
       </c>
-      <c r="F41" t="n">
+      <c r="Q41" t="n">
+        <v>1123223.93</v>
+      </c>
+      <c r="R41" t="n">
         <v>54.845</v>
       </c>
-      <c r="G41" t="n">
+      <c r="S41" t="n">
+        <v>1916657.9</v>
+      </c>
+      <c r="T41" t="n">
         <v>12.8</v>
       </c>
-      <c r="H41" t="n">
+      <c r="U41" t="n">
+        <v>447334.48</v>
+      </c>
+      <c r="V41" t="n">
         <v>0.207</v>
       </c>
-      <c r="I41" t="n">
+      <c r="W41" t="n">
+        <v>7228.68</v>
+      </c>
+      <c r="X41" t="n">
         <v>0.007</v>
       </c>
-      <c r="J41" t="n">
+      <c r="Y41" t="n">
+        <v>236.76</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.207</v>
       </c>
-      <c r="K41" t="n">
+      <c r="AA41" t="n">
         <v>0.007</v>
       </c>
-      <c r="L41" t="n">
-        <v>24.82</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="AB41" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1752.51</v>
+      </c>
+      <c r="AD41" t="n">
         <v>36.95</v>
       </c>
     </row>
@@ -2301,30 +4586,67 @@
         <v>4915200</v>
       </c>
       <c r="E42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>放大倍数估算</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>1228800</v>
+      </c>
+      <c r="P42" t="n">
         <v>30.038</v>
       </c>
-      <c r="F42" t="n">
+      <c r="Q42" t="n">
+        <v>369107</v>
+      </c>
+      <c r="R42" t="n">
         <v>55.22</v>
       </c>
-      <c r="G42" t="n">
+      <c r="S42" t="n">
+        <v>678539.75</v>
+      </c>
+      <c r="T42" t="n">
         <v>14.444</v>
       </c>
-      <c r="H42" t="n">
+      <c r="U42" t="n">
+        <v>177484.25</v>
+      </c>
+      <c r="V42" t="n">
         <v>0.295</v>
       </c>
-      <c r="I42" t="n">
+      <c r="W42" t="n">
+        <v>3623</v>
+      </c>
+      <c r="X42" t="n">
         <v>0.004</v>
       </c>
-      <c r="J42" t="n">
+      <c r="Y42" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.295</v>
       </c>
-      <c r="K42" t="n">
+      <c r="AA42" t="n">
         <v>0.004</v>
       </c>
-      <c r="L42" t="n">
-        <v>21.66</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="AB42" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>469.35</v>
+      </c>
+      <c r="AD42" t="n">
         <v>35.23</v>
       </c>
     </row>
@@ -2346,30 +4668,87 @@
         <v>4915200</v>
       </c>
       <c r="E43" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:34:10</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P43" t="n">
         <v>32.76</v>
       </c>
-      <c r="F43" t="n">
+      <c r="Q43" t="n">
+        <v>1144848.13</v>
+      </c>
+      <c r="R43" t="n">
         <v>53.511</v>
       </c>
-      <c r="G43" t="n">
+      <c r="S43" t="n">
+        <v>1870052.19</v>
+      </c>
+      <c r="T43" t="n">
         <v>13.621</v>
       </c>
-      <c r="H43" t="n">
+      <c r="U43" t="n">
+        <v>475993.26</v>
+      </c>
+      <c r="V43" t="n">
         <v>0.108</v>
       </c>
-      <c r="I43" t="n">
+      <c r="W43" t="n">
+        <v>3788.18</v>
+      </c>
+      <c r="X43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="n">
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.108</v>
       </c>
-      <c r="K43" t="n">
+      <c r="AA43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="AB43" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1310.96</v>
+      </c>
+      <c r="AD43" t="n">
         <v>37.97</v>
       </c>
     </row>
@@ -2391,30 +4770,87 @@
         <v>4915200</v>
       </c>
       <c r="E44" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:24:10</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P44" t="n">
         <v>30.092</v>
       </c>
-      <c r="F44" t="n">
+      <c r="Q44" t="n">
+        <v>1051620.36</v>
+      </c>
+      <c r="R44" t="n">
         <v>55.19</v>
       </c>
-      <c r="G44" t="n">
+      <c r="S44" t="n">
+        <v>1928709.97</v>
+      </c>
+      <c r="T44" t="n">
         <v>14.687</v>
       </c>
-      <c r="H44" t="n">
+      <c r="U44" t="n">
+        <v>513246.54</v>
+      </c>
+      <c r="V44" t="n">
         <v>0.008</v>
       </c>
-      <c r="I44" t="n">
+      <c r="W44" t="n">
+        <v>279.42</v>
+      </c>
+      <c r="X44" t="n">
         <v>0.024</v>
       </c>
-      <c r="J44" t="n">
+      <c r="Y44" t="n">
+        <v>825.46</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.008</v>
       </c>
-      <c r="K44" t="n">
+      <c r="AA44" t="n">
         <v>0.024</v>
       </c>
-      <c r="L44" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="M44" t="n">
+      <c r="AB44" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1685.78</v>
+      </c>
+      <c r="AD44" t="n">
         <v>35.29</v>
       </c>
     </row>
@@ -2436,30 +4872,87 @@
         <v>4915200</v>
       </c>
       <c r="E45" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:42:46</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P45" t="n">
         <v>28.876</v>
       </c>
-      <c r="F45" t="n">
+      <c r="Q45" t="n">
+        <v>1009124.2</v>
+      </c>
+      <c r="R45" t="n">
         <v>54.8</v>
       </c>
-      <c r="G45" t="n">
+      <c r="S45" t="n">
+        <v>1915083.76</v>
+      </c>
+      <c r="T45" t="n">
         <v>13.812</v>
       </c>
-      <c r="H45" t="n">
+      <c r="U45" t="n">
+        <v>482670.21</v>
+      </c>
+      <c r="V45" t="n">
         <v>0.867</v>
       </c>
-      <c r="I45" t="n">
+      <c r="W45" t="n">
+        <v>30281.98</v>
+      </c>
+      <c r="X45" t="n">
         <v>1.646</v>
       </c>
-      <c r="J45" t="n">
+      <c r="Y45" t="n">
+        <v>57521.61</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.867</v>
       </c>
-      <c r="K45" t="n">
+      <c r="AA45" t="n">
         <v>1.646</v>
       </c>
-      <c r="L45" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="M45" t="n">
+      <c r="AB45" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2835.46</v>
+      </c>
+      <c r="AD45" t="n">
         <v>34.51</v>
       </c>
     </row>
@@ -2481,30 +4974,87 @@
         <v>4915200</v>
       </c>
       <c r="E46" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:43:05</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P46" t="n">
         <v>29.709</v>
       </c>
-      <c r="F46" t="n">
+      <c r="Q46" t="n">
+        <v>1038224.5</v>
+      </c>
+      <c r="R46" t="n">
         <v>53.915</v>
       </c>
-      <c r="G46" t="n">
+      <c r="S46" t="n">
+        <v>1884141.26</v>
+      </c>
+      <c r="T46" t="n">
         <v>14.139</v>
       </c>
-      <c r="H46" t="n">
+      <c r="U46" t="n">
+        <v>494107.99</v>
+      </c>
+      <c r="V46" t="n">
         <v>0.241</v>
       </c>
-      <c r="I46" t="n">
+      <c r="W46" t="n">
+        <v>8435.24</v>
+      </c>
+      <c r="X46" t="n">
         <v>1.997</v>
       </c>
-      <c r="J46" t="n">
+      <c r="Y46" t="n">
+        <v>69772.77</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.241</v>
       </c>
-      <c r="K46" t="n">
+      <c r="AA46" t="n">
         <v>1.997</v>
       </c>
-      <c r="L46" t="n">
-        <v>53.98</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="AB46" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2071.44</v>
+      </c>
+      <c r="AD46" t="n">
         <v>35.53</v>
       </c>
     </row>
@@ -2526,30 +5076,87 @@
         <v>4915200</v>
       </c>
       <c r="E47" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:43:40</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P47" t="n">
         <v>29.39</v>
       </c>
-      <c r="F47" t="n">
+      <c r="Q47" t="n">
+        <v>1027074.68</v>
+      </c>
+      <c r="R47" t="n">
         <v>54.878</v>
       </c>
-      <c r="G47" t="n">
+      <c r="S47" t="n">
+        <v>1917801.18</v>
+      </c>
+      <c r="T47" t="n">
         <v>13.944</v>
       </c>
-      <c r="H47" t="n">
+      <c r="U47" t="n">
+        <v>487308.03</v>
+      </c>
+      <c r="V47" t="n">
         <v>0.43</v>
       </c>
-      <c r="I47" t="n">
+      <c r="W47" t="n">
+        <v>15038.25</v>
+      </c>
+      <c r="X47" t="n">
         <v>1.358</v>
       </c>
-      <c r="J47" t="n">
+      <c r="Y47" t="n">
+        <v>47459.62</v>
+      </c>
+      <c r="Z47" t="n">
         <v>0.43</v>
       </c>
-      <c r="K47" t="n">
+      <c r="AA47" t="n">
         <v>1.358</v>
       </c>
-      <c r="L47" t="n">
-        <v>64.62</v>
-      </c>
-      <c r="M47" t="n">
+      <c r="AB47" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2968.53</v>
+      </c>
+      <c r="AD47" t="n">
         <v>34.88</v>
       </c>
     </row>
@@ -2571,30 +5178,87 @@
         <v>4915200</v>
       </c>
       <c r="E48" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:38:40</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P48" t="n">
         <v>29.884</v>
       </c>
-      <c r="F48" t="n">
+      <c r="Q48" t="n">
+        <v>1044361.1</v>
+      </c>
+      <c r="R48" t="n">
         <v>55.163</v>
       </c>
-      <c r="G48" t="n">
+      <c r="S48" t="n">
+        <v>1927769.32</v>
+      </c>
+      <c r="T48" t="n">
         <v>14.435</v>
       </c>
-      <c r="H48" t="n">
+      <c r="U48" t="n">
+        <v>504458.65</v>
+      </c>
+      <c r="V48" t="n">
         <v>0.469</v>
       </c>
-      <c r="I48" t="n">
+      <c r="W48" t="n">
+        <v>16382.03</v>
+      </c>
+      <c r="X48" t="n">
         <v>0.049</v>
       </c>
-      <c r="J48" t="n">
+      <c r="Y48" t="n">
+        <v>1710.65</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.469</v>
       </c>
-      <c r="K48" t="n">
+      <c r="AA48" t="n">
         <v>0.049</v>
       </c>
-      <c r="L48" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="AB48" t="n">
+        <v>35.59</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>994.84</v>
+      </c>
+      <c r="AD48" t="n">
         <v>35.14</v>
       </c>
     </row>
@@ -2616,30 +5280,87 @@
         <v>4915200</v>
       </c>
       <c r="E49" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:39:08</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P49" t="n">
         <v>29.345</v>
       </c>
-      <c r="F49" t="n">
+      <c r="Q49" t="n">
+        <v>1025528.27</v>
+      </c>
+      <c r="R49" t="n">
         <v>55.07</v>
       </c>
-      <c r="G49" t="n">
+      <c r="S49" t="n">
+        <v>1924505.86</v>
+      </c>
+      <c r="T49" t="n">
         <v>14.631</v>
       </c>
-      <c r="H49" t="n">
+      <c r="U49" t="n">
+        <v>511291.31</v>
+      </c>
+      <c r="V49" t="n">
         <v>0.707</v>
       </c>
-      <c r="I49" t="n">
+      <c r="W49" t="n">
+        <v>24700.67</v>
+      </c>
+      <c r="X49" t="n">
         <v>0.248</v>
       </c>
-      <c r="J49" t="n">
+      <c r="Y49" t="n">
+        <v>8655.65</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.707</v>
       </c>
-      <c r="K49" t="n">
+      <c r="AA49" t="n">
         <v>0.248</v>
       </c>
-      <c r="L49" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="M49" t="n">
+      <c r="AB49" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>819.1799999999999</v>
+      </c>
+      <c r="AD49" t="n">
         <v>34.76</v>
       </c>
     </row>
@@ -2661,30 +5382,87 @@
         <v>4915200</v>
       </c>
       <c r="E50" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:39:43</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P50" t="n">
         <v>29.635</v>
       </c>
-      <c r="F50" t="n">
+      <c r="Q50" t="n">
+        <v>1035655.68</v>
+      </c>
+      <c r="R50" t="n">
         <v>55.206</v>
       </c>
-      <c r="G50" t="n">
+      <c r="S50" t="n">
+        <v>1929259.57</v>
+      </c>
+      <c r="T50" t="n">
         <v>14.482</v>
       </c>
-      <c r="H50" t="n">
+      <c r="U50" t="n">
+        <v>506101.76</v>
+      </c>
+      <c r="V50" t="n">
         <v>0.329</v>
       </c>
-      <c r="I50" t="n">
+      <c r="W50" t="n">
+        <v>11507.45</v>
+      </c>
+      <c r="X50" t="n">
         <v>0.348</v>
       </c>
-      <c r="J50" t="n">
+      <c r="Y50" t="n">
+        <v>12157.3</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.329</v>
       </c>
-      <c r="K50" t="n">
+      <c r="AA50" t="n">
         <v>0.348</v>
       </c>
-      <c r="L50" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="M50" t="n">
+      <c r="AB50" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>684.52</v>
+      </c>
+      <c r="AD50" t="n">
         <v>34.93</v>
       </c>
     </row>
@@ -2706,30 +5484,87 @@
         <v>4915200</v>
       </c>
       <c r="E51" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:40:13</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P51" t="n">
         <v>29.801</v>
       </c>
-      <c r="F51" t="n">
+      <c r="Q51" t="n">
+        <v>1041441.76</v>
+      </c>
+      <c r="R51" t="n">
         <v>54.723</v>
       </c>
-      <c r="G51" t="n">
+      <c r="S51" t="n">
+        <v>1912379.84</v>
+      </c>
+      <c r="T51" t="n">
         <v>14.435</v>
       </c>
-      <c r="H51" t="n">
+      <c r="U51" t="n">
+        <v>504468.6</v>
+      </c>
+      <c r="V51" t="n">
         <v>0.586</v>
       </c>
-      <c r="I51" t="n">
+      <c r="W51" t="n">
+        <v>20495.85</v>
+      </c>
+      <c r="X51" t="n">
         <v>0.455</v>
       </c>
-      <c r="J51" t="n">
+      <c r="Y51" t="n">
+        <v>15895.71</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.586</v>
       </c>
-      <c r="K51" t="n">
+      <c r="AA51" t="n">
         <v>0.455</v>
       </c>
-      <c r="L51" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="AB51" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>776.0700000000001</v>
+      </c>
+      <c r="AD51" t="n">
         <v>35.26</v>
       </c>
     </row>
@@ -2751,30 +5586,87 @@
         <v>4915200</v>
       </c>
       <c r="E52" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:40:55</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P52" t="n">
         <v>30.018</v>
       </c>
-      <c r="F52" t="n">
+      <c r="Q52" t="n">
+        <v>1049029.49</v>
+      </c>
+      <c r="R52" t="n">
         <v>54.995</v>
       </c>
-      <c r="G52" t="n">
+      <c r="S52" t="n">
+        <v>1921897.93</v>
+      </c>
+      <c r="T52" t="n">
         <v>13.872</v>
       </c>
-      <c r="H52" t="n">
+      <c r="U52" t="n">
+        <v>484768.36</v>
+      </c>
+      <c r="V52" t="n">
         <v>1.103</v>
       </c>
-      <c r="I52" t="n">
+      <c r="W52" t="n">
+        <v>38543.74</v>
+      </c>
+      <c r="X52" t="n">
         <v>0.013</v>
       </c>
-      <c r="J52" t="n">
+      <c r="Y52" t="n">
+        <v>442.24</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.103</v>
       </c>
-      <c r="K52" t="n">
+      <c r="AA52" t="n">
         <v>0.013</v>
       </c>
-      <c r="L52" t="n">
-        <v>25.29</v>
-      </c>
-      <c r="M52" t="n">
+      <c r="AB52" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1819.38</v>
+      </c>
+      <c r="AD52" t="n">
         <v>35.31</v>
       </c>
     </row>
@@ -2796,30 +5688,87 @@
         <v>4915200</v>
       </c>
       <c r="E53" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:41:20</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P53" t="n">
         <v>31.033</v>
       </c>
-      <c r="F53" t="n">
+      <c r="Q53" t="n">
+        <v>1084515.95</v>
+      </c>
+      <c r="R53" t="n">
         <v>54.006</v>
       </c>
-      <c r="G53" t="n">
+      <c r="S53" t="n">
+        <v>1887339.32</v>
+      </c>
+      <c r="T53" t="n">
         <v>14.701</v>
       </c>
-      <c r="H53" t="n">
+      <c r="U53" t="n">
+        <v>513739.97</v>
+      </c>
+      <c r="V53" t="n">
         <v>0.229</v>
       </c>
-      <c r="I53" t="n">
+      <c r="W53" t="n">
+        <v>7997.98</v>
+      </c>
+      <c r="X53" t="n">
         <v>0.031</v>
       </c>
-      <c r="J53" t="n">
+      <c r="Y53" t="n">
+        <v>1088.53</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.229</v>
       </c>
-      <c r="K53" t="n">
+      <c r="AA53" t="n">
         <v>0.031</v>
       </c>
-      <c r="L53" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="AB53" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1771.46</v>
+      </c>
+      <c r="AD53" t="n">
         <v>36.49</v>
       </c>
     </row>
@@ -2841,30 +5790,67 @@
         <v>4915200</v>
       </c>
       <c r="E54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>放大倍数估算</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>1228800</v>
+      </c>
+      <c r="P54" t="n">
         <v>30.763</v>
       </c>
-      <c r="F54" t="n">
+      <c r="Q54" t="n">
+        <v>378020</v>
+      </c>
+      <c r="R54" t="n">
         <v>54.544</v>
       </c>
-      <c r="G54" t="n">
+      <c r="S54" t="n">
+        <v>670234.5</v>
+      </c>
+      <c r="T54" t="n">
         <v>14.499</v>
       </c>
-      <c r="H54" t="n">
+      <c r="U54" t="n">
+        <v>178167.5</v>
+      </c>
+      <c r="V54" t="n">
         <v>0.167</v>
       </c>
-      <c r="I54" t="n">
+      <c r="W54" t="n">
+        <v>2055.25</v>
+      </c>
+      <c r="X54" t="n">
         <v>0.026</v>
       </c>
-      <c r="J54" t="n">
+      <c r="Y54" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.167</v>
       </c>
-      <c r="K54" t="n">
+      <c r="AA54" t="n">
         <v>0.026</v>
       </c>
-      <c r="L54" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="M54" t="n">
+      <c r="AB54" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>600.97</v>
+      </c>
+      <c r="AD54" t="n">
         <v>36.06</v>
       </c>
     </row>
@@ -2886,30 +5872,87 @@
         <v>4915200</v>
       </c>
       <c r="E55" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:41:52</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P55" t="n">
         <v>31.56</v>
       </c>
-      <c r="F55" t="n">
+      <c r="Q55" t="n">
+        <v>1102935.7</v>
+      </c>
+      <c r="R55" t="n">
         <v>54.584</v>
       </c>
-      <c r="G55" t="n">
+      <c r="S55" t="n">
+        <v>1907550.77</v>
+      </c>
+      <c r="T55" t="n">
         <v>13.77</v>
       </c>
-      <c r="H55" t="n">
+      <c r="U55" t="n">
+        <v>481231.16</v>
+      </c>
+      <c r="V55" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="I55" t="n">
+      <c r="W55" t="n">
+        <v>2422.36</v>
+      </c>
+      <c r="X55" t="n">
         <v>0.016</v>
       </c>
-      <c r="J55" t="n">
+      <c r="Y55" t="n">
+        <v>541.78</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="K55" t="n">
+      <c r="AA55" t="n">
         <v>0.016</v>
       </c>
-      <c r="L55" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="M55" t="n">
+      <c r="AB55" t="n">
+        <v>50.24</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1982.11</v>
+      </c>
+      <c r="AD55" t="n">
         <v>36.64</v>
       </c>
     </row>
@@ -2931,30 +5974,87 @@
         <v>4915200</v>
       </c>
       <c r="E56" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:42:13</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P56" t="n">
         <v>30.235</v>
       </c>
-      <c r="F56" t="n">
+      <c r="Q56" t="n">
+        <v>1056620.07</v>
+      </c>
+      <c r="R56" t="n">
         <v>55.198</v>
       </c>
-      <c r="G56" t="n">
+      <c r="S56" t="n">
+        <v>1928990.1</v>
+      </c>
+      <c r="T56" t="n">
         <v>14.216</v>
       </c>
-      <c r="H56" t="n">
+      <c r="U56" t="n">
+        <v>496817.59</v>
+      </c>
+      <c r="V56" t="n">
         <v>0.332</v>
       </c>
-      <c r="I56" t="n">
+      <c r="W56" t="n">
+        <v>11603.44</v>
+      </c>
+      <c r="X56" t="n">
         <v>0.019</v>
       </c>
-      <c r="J56" t="n">
+      <c r="Y56" t="n">
+        <v>650.5599999999999</v>
+      </c>
+      <c r="Z56" t="n">
         <v>0.332</v>
       </c>
-      <c r="K56" t="n">
+      <c r="AA56" t="n">
         <v>0.019</v>
       </c>
-      <c r="L56" t="n">
-        <v>28.55</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="AB56" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2317.33</v>
+      </c>
+      <c r="AD56" t="n">
         <v>35.39</v>
       </c>
     </row>
@@ -2976,30 +6076,87 @@
         <v>4915200</v>
       </c>
       <c r="E57" t="n">
+        <v>0.843205</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>XML元数据</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2158.61</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1618.95</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>AxioCamEL</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026/5/7 19:37:49</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>3494681.76</v>
+      </c>
+      <c r="P57" t="n">
         <v>30.126</v>
       </c>
-      <c r="F57" t="n">
+      <c r="Q57" t="n">
+        <v>1052809.85</v>
+      </c>
+      <c r="R57" t="n">
         <v>55.145</v>
       </c>
-      <c r="G57" t="n">
+      <c r="S57" t="n">
+        <v>1927132.27</v>
+      </c>
+      <c r="T57" t="n">
         <v>14.674</v>
       </c>
-      <c r="H57" t="n">
+      <c r="U57" t="n">
+        <v>512797.91</v>
+      </c>
+      <c r="V57" t="n">
         <v>0.006</v>
       </c>
-      <c r="I57" t="n">
+      <c r="W57" t="n">
+        <v>218.28</v>
+      </c>
+      <c r="X57" t="n">
         <v>0.049</v>
       </c>
-      <c r="J57" t="n">
+      <c r="Y57" t="n">
+        <v>1723.45</v>
+      </c>
+      <c r="Z57" t="n">
         <v>0.006</v>
       </c>
-      <c r="K57" t="n">
+      <c r="AA57" t="n">
         <v>0.049</v>
       </c>
-      <c r="L57" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="M57" t="n">
+      <c r="AB57" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2671.09</v>
+      </c>
+      <c r="AD57" t="n">
         <v>35.33</v>
       </c>
     </row>
